--- a/System_Design_Roadmap.xlsx
+++ b/System_Design_Roadmap.xlsx
@@ -433,12 +433,12 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Primary Video Resource (Coder Army)</t>
+          <t>Primary Video Resource</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -512,32 +512,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Networking &amp; Web</t>
+          <t>System Design Intro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>How the Internet &amp; Web Works</t>
+          <t>Introduction to System Design: HLD vs LLD &amp; Scalability Overview</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DNS, IP, TCP 3-Way Handshake, SSL/TLS Handshake</t>
+          <t>What is a System, Monolith vs Microservices, Vertical vs Horizontal scaling, System Design interview framework</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=1</t>
+          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7_LPdttKXPc</t>
+          <t>https://www.youtube.com/watch?v=i7twT3x5yv8</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Write down step-by-step trace of typing 'google.com' in browser</t>
+          <t>Write down the core difference between High-Level Design (HLD) and Low-Level Design (LLD)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Client-Server Architecture &amp; OSI Model</t>
+          <t>How the Internet Works &amp; Client-Server Architecture (DNS, IP, Routing)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7 Layers, Client/Server roles, Request-Response cycle</t>
+          <t>DNS resolution, IP routing, Ports, Client/Server roles, Request-Response lifecycle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=2</t>
+          <t>https://www.youtube.com/watch?v=7_LPdttKXPc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Map OSI layers to real web protocols (HTTP, TCP, IP, Ethernet)</t>
+          <t>Write down the step-by-step trace of typing 'google.com' in a browser until the page renders</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -609,27 +609,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HTTP Evolution: HTTP/1.1 vs HTTP/2 vs HTTP/3</t>
+          <t>OSI &amp; TCP/IP Model: TCP 3-Way Handshake vs UDP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persistent connections, Multiplexing, Head-of-line blocking, QUIC/UDP</t>
+          <t>7 Layers vs 4 Layers, TCP 3-Way Handshake (SYN, SYN-ACK, ACK), Connection-oriented TCP vs Fast UDP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=3</t>
+          <t>https://www.youtube.com/watch?v=a-sBfyiXysI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a-sBfyiXysI</t>
+          <t>https://www.youtube.com/watch?v=bW_kWXqEgPE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Compare HTTP/1.1 vs HTTP/2 performance trade-offs in a table</t>
+          <t>Map real web protocols (HTTP, TCP, IP, Ethernet) to their respective OSI layers</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -650,32 +650,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Real-Time Protocols</t>
+          <t>Web Protocols</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WebSockets vs Long Polling vs SSE vs WebRTC</t>
+          <t>HTTP &amp; HTTPS: Evolution (HTTP/1.1 vs HTTP/2 vs HTTP/3) &amp; SSL/TLS Handshake</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Full-duplex real-time communication, Server-Sent Events, Video streaming</t>
+          <t>Multiplexing, Head-of-line blocking, QUIC protocol, Symmetric vs Asymmetric encryption, TLS Handshake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=4</t>
+          <t>https://www.youtube.com/watch?v=UMwOxv_y_3E</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=i5OVcTbfET8</t>
+          <t>https://www.youtube.com/watch?v=86cQjh5uU0E</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Select the right protocol for: (1) Chat App, (2) Stock Ticker, (3) Video Call</t>
+          <t>Create a comparison table showing how HTTP/2 multiplexing solves HTTP/1.1 HOL blocking</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -701,27 +701,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>REST Architecture &amp; Constraints</t>
+          <t>REST Architecture &amp; 6 Guiding Constraints</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Statelessness, Uniform Interface, Client-Server, Cacheability</t>
+          <t>Statelessness, Client-Server separation, Cacheability, Uniform Interface, Layered System, Code-on-Demand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=5</t>
+          <t>https://www.youtube.com/watch?v=-mN3VyJuCjM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-mN3VyJuCjM</t>
+          <t>https://www.youtube.com/watch?v=lsMQRaeKNDk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Explain the 6 REST architectural constraints in plain English</t>
+          <t>Explain why statelessness in REST makes horizontal backend scaling much easier</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -747,27 +747,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HTTP Methods &amp; Idempotency Deep Dive</t>
+          <t>HTTP Methods &amp; Idempotency Deep Dive (GET, POST, PUT, PATCH, DELETE)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GET, POST, PUT, PATCH, DELETE. Why PUT is idempotent but POST is not</t>
+          <t>Safe vs Idempotent methods. Why PUT is idempotent but POST is not. Handling double-payment submissions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=6</t>
+          <t>https://www.youtube.com/watch?v=6UXF9gcsngA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6UXF9gcsngA</t>
+          <t>https://www.youtube.com/watch?v=0kH_Fw-7GgI</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Design REST endpoints for an E-Commerce Cart &amp; Order Placement flow</t>
+          <t>Design REST endpoints for an E-Commerce Cart &amp; Checkout order flow with correct methods</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HTTP Status Codes &amp; Error Handling</t>
+          <t>HTTP Status Codes &amp; API Error Handling (2xx, 3xx, 4xx, 5xx)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2xx (Success), 3xx (Redirects), 4xx (Client errors), 5xx (Server errors)</t>
+          <t>200 OK, 201 Created, 204 No Content, 301 vs 302, 400, 401 vs 403, 404, 429, 500, 502 Bad Gateway, 504</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=7</t>
+          <t>https://www.youtube.com/watch?v=0kH_Fw-7GgI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0kH_Fw-7GgI</t>
+          <t>https://www.youtube.com/watch?v=7Q17ubqLfaM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Flashcard drill: Match 10 real-world API error scenarios to exact status codes</t>
+          <t>Flashcard drill: Explain the difference between 401 Unauthorized and 403 Forbidden with examples</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>REST API Design</t>
+          <t>Real-Time Protocols</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>API Security, Headers, Pagination &amp; Versioning</t>
+          <t>WebSockets vs Long Polling vs Server-Sent Events (SSE) vs WebRTC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JWT vs Sessions, OAuth 2.0, Offset vs Cursor Pagination, Rate limiting headers</t>
+          <t>Full-duplex bidirectional communication, Server-Sent Events for one-way streams, WebRTC for P2P audio/video</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=8</t>
+          <t>https://www.youtube.com/watch?v=i5OVcTbfET8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7Q17ubqLfaM</t>
+          <t>https://www.youtube.com/watch?v=1BfCnjr_Vjg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Draft a complete OpenAPI/Swagger JSON specification for a User Auth API</t>
+          <t>Select the optimal protocol for: (1) WhatsApp Chat, (2) Stock Ticker, (3) Live Video Call</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -885,27 +885,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Relational Databases (SQL / RDBMS) Overview</t>
+          <t>Relational Databases (SQL / RDBMS) Architecture</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PostgreSQL/MySQL architecture, Tables, Foreign Keys, Schema constraints</t>
+          <t>PostgreSQL/MySQL storage engines, Tables, Foreign Keys, Schema integrity constraints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=9</t>
+          <t>https://www.youtube.com/watch?v=Qn067qR-w8Q</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Qn067qR-w8Q</t>
+          <t>https://www.youtube.com/watch?v=UrYLYV7WSHM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Design a normalized relational schema for a Food Delivery App</t>
+          <t>Design a normalized relational schema for a Food Delivery App (Users, Restaurants, Orders)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -936,22 +936,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atomicity, Consistency, Isolation, Durability with banking transactions</t>
+          <t>Atomicity, Consistency, Isolation, Durability with banking money transfer transactions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=10</t>
+          <t>https://www.youtube.com/watch?v=gaT_Yw10hRk</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gaT_Yw10hRk</t>
+          <t>https://www.youtube.com/watch?v=pomxJODBcCo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Explain how Rollback and Write-Ahead Logging (WAL) ensure Atomicity and Durability</t>
+          <t>Explain how Write-Ahead Logging (WAL) guarantees Durability even if the power fails</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transaction Isolation Levels &amp; Concurrency</t>
+          <t>Transaction Isolation Levels &amp; Concurrency Anomalies</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dirty Reads, Non-repeatable Reads, Phantom Reads. Read Committed vs Repeatable Read</t>
+          <t>Dirty Reads, Non-repeatable Reads, Phantom Reads. Read Committed vs Repeatable Read vs Serializable</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=11</t>
+          <t>https://www.youtube.com/watch?v=Kz_z7QxsmG0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Kz_z7QxsmG0</t>
+          <t>https://www.youtube.com/watch?v=rL_pZ1QxY8M</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Simulate two concurrent bank transfers and show which isolation level prevents double spending</t>
+          <t>Simulate two concurrent banking transactions and show which isolation level prevents double spending</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Database Indexing Deep Dive (B-Trees &amp; B+ Trees)</t>
+          <t>Database Indexing Deep Dive (How B+ Trees Work)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>How B+ Trees store data, Clustered vs Non-Clustered index, range query speed</t>
+          <t>How B+ Trees organize data on disk, Clustered Index (Primary Key) vs Non-Clustered (Secondary) Index</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=12</t>
+          <t>https://www.youtube.com/watch?v=fsG1XaZEa78</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=fsG1XaZEa78</t>
+          <t>https://www.youtube.com/watch?v=aZjYr87r1b8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Given a query with WHERE user_id = 5 AND status = 'ACTIVE' ORDER BY created_at, design optimal composite index</t>
+          <t>Given a query with WHERE user_id = ? AND status = 'ACTIVE' ORDER BY created_at, design the composite index</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1069,27 +1069,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Indexing Trade-offs &amp; Query Optimization</t>
+          <t>Indexing Trade-offs &amp; Query Optimization (EXPLAIN Plans)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Why indexing slows down INSERT/UPDATE/DELETE, EXPLAIN ANALYZE queries</t>
+          <t>Why indexing speeds up SELECT queries but slows down INSERT/UPDATE/DELETE. Reading EXPLAIN query plans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=13</t>
+          <t>https://www.youtube.com/watch?v=BIflr3N8v4M</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BIflr3N8v4M</t>
+          <t>https://www.youtube.com/watch?v=HubezKbFL7E</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Analyze a slow SQL query with EXPLAIN plan and fix it using indexing</t>
+          <t>Analyze a slow SQL query and explain why adding too many indexes degrades write throughput</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1120,22 +1120,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Reducing data redundancy vs optimizing high-throughput reads</t>
+          <t>Eliminating data redundancy vs intentionally denormalizing data to eliminate expensive JOINs on reads</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=14</t>
+          <t>https://www.youtube.com/watch?v=UrYLYV7WSHM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UrYLYV7WSHM</t>
+          <t>https://www.youtube.com/watch?v=GFQaEYEc8_8</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Demonstrate when you would denormalize a Comment count in a Social Media post table</t>
+          <t>Demonstrate when you would denormalize a Comment Count column in a high-traffic Social Media post table</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1161,27 +1161,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Introduction to NoSQL &amp; The 4 Main Types</t>
+          <t>Introduction to NoSQL: Document, Key-Value, Columnar &amp; Graph</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Document (MongoDB), Key-Value (Redis), Columnar (Cassandra), Graph (Neo4j)</t>
+          <t>MongoDB (Document), Redis (Key-Value), Cassandra (Column-family), Neo4j (Graph). When to choose SQL vs NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=15</t>
+          <t>https://www.youtube.com/watch?v=0buKQHokLK8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0buKQHokLK8</t>
+          <t>https://www.youtube.com/watch?v=ku1pwfO3UfA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Create a decision matrix: SQL vs MongoDB vs Redis vs Cassandra</t>
+          <t>Build a decision matrix comparing SQL vs MongoDB vs Redis vs Cassandra across 5 dimensions</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1207,27 +1207,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Database Replication (Master-Slave / Leader-Follower)</t>
+          <t>Database Replication: Read Replicas &amp; Master-Slave Sync</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Read Replicas, Synchronous vs Asynchronous replication, Replication lag</t>
+          <t>Leader-Follower architecture, Synchronous vs Asynchronous replication, Handling Replication Lag</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=16</t>
+          <t>https://www.youtube.com/watch?v=mprR3c_Y4pA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mprR3c_Y4pA</t>
+          <t>https://www.youtube.com/watch?v=gT8v8Zq8hS8</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Explain how to solve 'Read-Your-Own-Writes' consistency problem with read replicas</t>
+          <t>Explain how to solve the 'Read-Your-Own-Writes' consistency problem when using read replicas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Range-based, Hash-based, Directory-based sharding, Cross-shard queries</t>
+          <t>Range-based, Hash-based, and Directory-based sharding. Handling cross-shard JOINs and hot partitions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=17</t>
+          <t>https://www.youtube.com/watch?v=5faMjKuB9bc</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=5faMjKuB9bc</t>
+          <t>https://www.youtube.com/watch?v=Kz_z7QxsmG0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1299,27 +1299,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Consistent Hashing &amp; Hash Rings</t>
+          <t>Consistent Hashing &amp; Distributed Hash Rings</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Virtual nodes, Minimizing re-balancing keys during node additions/failures</t>
+          <t>Virtual nodes, Minimizing key re-balancing when servers are added or removed in distributed caches</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=18</t>
+          <t>https://www.youtube.com/watch?v=zaRkONvyGr8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zaRkONvyGr8</t>
+          <t>https://www.youtube.com/watch?v=tHEyzVbl4bg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Implement basic Consistent Hashing logic in C++ / Python</t>
+          <t>Trace what happens in a consistent hash ring when Server 2 crashes and goes offline</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Scale-up limits, Scale-out benefits, Decoupling session state to Redis</t>
+          <t>Scale-up limits, Scale-out benefits, Decoupling session state to Redis, Auto-scaling groups</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=19</t>
+          <t>https://www.youtube.com/watch?v=xpDnVSmNFX0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xpDnVSmNFX0</t>
+          <t>https://www.youtube.com/watch?v=M7WzV8C3v-Y</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1391,27 +1391,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Load Balancers &amp; Routing Algorithms</t>
+          <t>Load Balancers &amp; Traffic Routing Algorithms (L4 vs L7)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>L4 vs L7, Round Robin, Least Connections, IP Hash, Health checks</t>
+          <t>L4 Transport vs L7 Application load balancing. Round Robin, Least Connections, IP Hash algorithms</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=20</t>
+          <t>https://www.youtube.com/watch?v=K0Ta65OqQkY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K0Ta65OqQkY</t>
+          <t>https://www.youtube.com/watch?v=sCR3Xh8Jpxg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Draw a diagram showing HAProxy L7 load balancer routing traffic based on URL path</t>
+          <t>Draw a diagram showing HAProxy L7 load balancer routing traffic based on URL paths (/api vs /static)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SSL Termination, Compression, Rate Limiting, Authentication routing</t>
+          <t>SSL Termination, Response Compression, Rate Limiting, Authentication routing, Forward vs Reverse proxy</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=21</t>
+          <t>https://www.youtube.com/watch?v=Xh7b_KqQvI8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Xh7b_KqQvI8</t>
+          <t>https://www.youtube.com/watch?v=1vL3MXva9ms</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Explain the 5 core responsibilities of an API Gateway in Microservices</t>
+          <t>Explain the 5 core responsibilities of an API Gateway in a microservices architecture</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1483,27 +1483,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Caching Fundamentals &amp; Caching Locations</t>
+          <t>Caching Fundamentals: CDN, Edge Caching &amp; In-Memory Redis</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Client Cache, CDN (Edge), Reverse Proxy Cache, Redis, DB Cache</t>
+          <t>Client Cache, CDN (Cloudflare), Reverse Proxy Cache, Application Cache, Redis/Memcached DB cache</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=22</t>
+          <t>https://www.youtube.com/watch?v=dGAgxozNWFE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dGAgxozNWFE</t>
+          <t>https://www.youtube.com/watch?v=G1rOthIU-uo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Calculate cache hit ratio and latency savings for a 95% cache hit rate</t>
+          <t>Calculate cache hit ratio and latency savings for a 95% cache hit rate system</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Read-heavy vs Write-heavy patterns, Cache-Aside (Lazy loading), Write-Back dirty buffer</t>
+          <t>Lazy loading (Cache-Aside), Synchronous write-through, Asynchronous write-back buffer trade-offs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=23</t>
+          <t>https://www.youtube.com/watch?v=6ph8iY7Z2lU</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6ph8iY7Z2lU</t>
+          <t>https://www.youtube.com/watch?v=VwZZy9P_e-0</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1580,22 +1580,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Least Recently Used, Least Frequently Used, TTL expirations</t>
+          <t>Least Recently Used (LRU), Least Frequently Used (LFU), Time To Live (TTL) expiration strategies</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=24</t>
+          <t>https://www.youtube.com/watch?v=S6ifbS1wO60</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=S6ifbS1wO60</t>
+          <t>https://www.youtube.com/watch?v=R0UkJSzM_4k</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Explain why Hash Map + Doubly Linked List enables O(1) LRU Cache operations</t>
+          <t>Explain why Hash Map + Doubly Linked List enables O(1) LRU Cache get and put operations</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1621,27 +1621,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cache Pitfalls: Penetration, Avalanche, Stampede (Thundering Herd)</t>
+          <t>Cache Pitfalls: Penetration, Avalanche &amp; Stampede (Thundering Herd)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Null caching, Bloom filters, Jittered TTLs, Mutex locking</t>
+          <t>Null caching, Bloom filters, Jittered TTLs, Mutex locking to prevent DB crashes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=25</t>
+          <t>https://www.youtube.com/watch?v=d_6w4v3u2Hk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=d_6w4v3u2Hk</t>
+          <t>https://www.youtube.com/watch?v=VbTx6j_Fq-8</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Propose a concrete solution for Cache Avalanche when 100,000 keys expire at midnight</t>
+          <t>Propose a concrete architectural fix for Cache Avalanche when 100,000 keys expire at midnight</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Message Queues &amp; Decoupled Architecture</t>
+          <t>Message Queues &amp; Decoupled Event-Driven Architecture</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Point-to-point queues, Pub-Sub, Backpressure, Consumer groups</t>
+          <t>Point-to-point queues, Pub-Sub, Backpressure handling, Decoupling producers and consumers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=26</t>
+          <t>https://www.youtube.com/watch?v=oUJbuFMyBDk</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=oUJbuFMyBDk</t>
+          <t>https://www.youtube.com/watch?v=iJLL-KPqBpM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1718,22 +1718,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Queue-based push model vs Distributed log-based pull model, Topic partitions, Offsets</t>
+          <t>Traditional push queue model vs Distributed append-only log pull model, Topic partitions, Consumer groups</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=27</t>
+          <t>https://www.youtube.com/watch?v=Ch5VhJzaoaI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ch5VhJzaoaI</t>
+          <t>https://www.youtube.com/watch?v=quv0u9y6l5w</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Create a comparison table: RabbitMQ vs Kafka throughput, latency, and retention</t>
+          <t>Create a comparison table: RabbitMQ vs Kafka throughput, latency, ordering, and retention</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1764,22 +1764,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Consistency vs Availability over network partitions. Real-world CP vs AP systems</t>
+          <t>Consistency vs Availability over network partitions. Why P is mandatory. Real-world CP vs AP systems</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=28</t>
+          <t>https://www.youtube.com/watch?v=k-Yaq8AHlFA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k-Yaq8AHlFA</t>
+          <t>https://www.youtube.com/watch?v=BHqjEjzAicA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Classify MySQL, MongoDB, Cassandra, and Spanner into CP vs AP models</t>
+          <t>Classify MySQL, MongoDB, Cassandra, and Spanner into CP vs AP models with justification</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>S and O principles with code examples, decoupling business logic</t>
+          <t>Single Responsibility (SRP) and Open/Closed (OCP) principles with clean C++ examples</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=29</t>
+          <t>https://www.youtube.com/watch?v=yYw_2F0O46Q</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yYw_2F0O46Q</t>
+          <t>https://www.youtube.com/watch?v=pTB30aXS77U</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Refactor a messy C++ Invoice generator class to adhere to SRP and OCP</t>
+          <t>Refactor a messy C++ Invoice generator class to strictly adhere to SRP and OCP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>L, I, D principles, Dependency Injection, Interface segregation</t>
+          <t>Liskov Substitution (LSP), Interface Segregation (ISP), Dependency Inversion (DIP) &amp; Dependency Injection</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=30</t>
+          <t>https://www.youtube.com/watch?v=v-27FT7-5pk</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=v-27FT7-5pk</t>
+          <t>https://www.youtube.com/watch?v=TMuno5_b7Qk</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Creational Patterns: Singleton &amp; Factory Pattern</t>
+          <t>Creational Patterns: Singleton &amp; Factory Method in C++</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Thread-safe Singleton in C++, Factory Method, Abstract Factory</t>
+          <t>Thread-safe Meyers' Singleton in C++, Factory Method, Abstract Factory for decoupling object creation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=31</t>
+          <t>https://www.youtube.com/watch?v=EJavaYOFgkE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EJavaYOFgkE</t>
+          <t>https://www.youtube.com/watch?v=PPup1yeU45I</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Constructing complex objects step-by-step, cloning objects</t>
+          <t>Constructing complex objects step-by-step, method chaining, cloning objects</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=32</t>
+          <t>https://www.youtube.com/watch?v=M7Xi1yO_58o</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M7Xi1yO_58o</t>
+          <t>https://www.youtube.com/watch?v=v9ejT8FO-7I</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrapping incompatible interfaces, adding dynamic behavior, simplifying APIs</t>
+          <t>Wrapping incompatible interfaces, adding dynamic behavior at runtime, simplifying complex subsystems</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=33</t>
+          <t>https://www.youtube.com/watch?v=2PKQtNXTEVU</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2PKQtNXTEVU</t>
+          <t>https://www.youtube.com/watch?v=qG286LQM6BU</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Implement a Pizza pricing calculator in C++ using the Decorator pattern</t>
+          <t>Implement a Coffee/Pizza pricing calculator in C++ using the Decorator pattern</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2035,27 +2035,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Behavioral Patterns: Strategy &amp; Observer Pattern</t>
+          <t>Behavioral Patterns: Strategy &amp; Observer (Pub-Sub) Pattern</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Interchangeable algorithms, Event listener / Pub-Sub pattern</t>
+          <t>Interchangeable algorithms at runtime, Event listener / Pub-Sub pattern for decoupling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=34</t>
+          <t>https://www.youtube.com/watch?v=_BpmXJYXWU4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_BpmXJYXWU4</t>
+          <t>https://www.youtube.com/watch?v=v9ejT8FO-7I</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Implement a Payment Processor in C++ using Strategy (CreditCard, UPI, PayPal)</t>
+          <t>Implement a Payment Processor in C++ using Strategy pattern (CreditCard, UPI, PayPal)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Requirements, Capacity Estimations, High-Level Design, Deep Dives</t>
+          <t>Step 1 Requirements, Step 2 Capacity Estimations, Step 3 High-Level Design, Step 4 Component Deep-Dives</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=35</t>
+          <t>https://www.youtube.com/watch?v=i7twT3x5yv8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=i7twT3x5yv8</t>
+          <t>https://www.youtube.com/watch?v=bUHFg8CZFCA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2132,17 +2132,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Base62 encoding, Hash collisions, DB Schema, Redirection Caching</t>
+          <t>Base62 encoding, Hash collisions, Relational DB Schema, Redis Redirection Caching</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=36</t>
+          <t>https://www.youtube.com/watch?v=JQDHz72OA3c</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JQDHz72OA3c</t>
+          <t>https://www.youtube.com/watch?v=fMZMm_0ZhK4</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2178,17 +2178,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Token Bucket, Leaky Bucket, Sliding Window Counter with Redis</t>
+          <t>Token Bucket, Leaky Bucket, Sliding Window Counter algorithms with Redis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=37</t>
+          <t>https://www.youtube.com/watch?v=CRGPbCbRpHU</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CRGPbCbRpHU</t>
+          <t>https://www.youtube.com/watch?v=FU4WlwfS3G0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2219,22 +2219,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Design a Chat Application (WhatsApp / Messenger)</t>
+          <t>Design a Real-Time Chat App (WhatsApp / Messenger)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WebSockets, Gateway servers, Cassandra message storage, Online/Offline presence</t>
+          <t>WebSockets, Gateway servers, Cassandra message storage, Online/Offline presence indicator</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=38</t>
+          <t>https://www.youtube.com/watch?v=vvhC64hQZMk</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vvhC64hQZMk</t>
+          <t>https://www.youtube.com/watch?v=zKPNUMkwOJE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2270,17 +2270,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fan-out on write vs Fan-out on read, News Feed ranking, CDN caching for media</t>
+          <t>Fan-out on write vs Fan-out on read, Hybrid fan-out for celebrities, News Feed ranking, CDN media delivery</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=39</t>
+          <t>https://www.youtube.com/watch?v=S2y9_710_0Q</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=S2y9_710_0Q</t>
+          <t>https://www.youtube.com/watch?v=KmAyPUv97nM</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Geohashing, QuadTrees for spatial proximity, Driver location tracking, Matching service</t>
+          <t>Geohashing, QuadTrees for spatial proximity, Driver location tracking, Matching engine</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AK0hu0Zxua4&amp;list=PLQEaRBV9gAFvzp6XhcNFpk1WdOcyVo9qT&amp;index=40</t>
+          <t>https://www.youtube.com/watch?v=Tp8KpMe-ZKw</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Tp8KpMe-ZKw</t>
+          <t>https://www.youtube.com/watch?v=umWABit-wbk</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/System_Design_Roadmap.xlsx
+++ b/System_Design_Roadmap.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4b2kR4p1HVs</t>
+          <t>https://www.youtube.com/watch?v=mpQZVYPuDGU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,12 +619,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a-sBfyiXysI</t>
+          <t>https://www.youtube.com/watch?v=vv4y_uOneC0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bW_kWXqEgPE</t>
+          <t>https://www.youtube.com/watch?v=3ZqmqNPHT40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UMwOxv_y_3E</t>
+          <t>https://www.youtube.com/watch?v=UMwQjFzTQXw</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=86cQjh5uU0E</t>
+          <t>https://www.youtube.com/watch?v=hExRDVZHhig</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6UXF9gcsngA</t>
+          <t>https://www.youtube.com/watch?v=tkfVQK6UxDI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0kH_Fw-7GgI</t>
+          <t>https://www.youtube.com/watch?v=XAccGbtl3Z8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0kH_Fw-7GgI</t>
+          <t>https://www.youtube.com/watch?v=wJa5CTIFj7U</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7Q17ubqLfaM</t>
+          <t>https://www.youtube.com/watch?v=qmpUfWN7hh4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=i5OVcTbfET8</t>
+          <t>https://www.youtube.com/watch?v=1BfCnjr_Vjg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BfCnjr_Vjg</t>
+          <t>https://www.youtube.com/watch?v=X_DdIXrmWOo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Qn067qR-w8Q</t>
+          <t>https://www.youtube.com/watch?v=zsjvFFKOm3c</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UrYLYV7WSHM</t>
+          <t>https://www.youtube.com/watch?v=ztHopE5Wnpc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gaT_Yw10hRk</t>
+          <t>https://www.youtube.com/watch?v=-GS0OxFJsYQ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pomxJODBcCo</t>
+          <t>https://www.youtube.com/watch?v=pomxJOFVcQs</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Kz_z7QxsmG0</t>
+          <t>https://www.youtube.com/watch?v=pomxJOFVcQs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rL_pZ1QxY8M</t>
+          <t>https://www.youtube.com/watch?v=t5hsV9lC1rU</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aZjYr87r1b8</t>
+          <t>https://www.youtube.com/watch?v=KcApkM5WYGw</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BIflr3N8v4M</t>
+          <t>https://www.youtube.com/watch?v=OhJ3xcjtpis</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=HubezKbFL7E</t>
+          <t>https://www.youtube.com/watch?v=1nENigGr-a0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UrYLYV7WSHM</t>
+          <t>https://www.youtube.com/watch?v=5GDTIUVlHB8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=GFQaEYEc8_8</t>
+          <t>https://www.youtube.com/watch?v=W_5vn8TBLys</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ku1pwfO3UfA</t>
+          <t>https://www.youtube.com/watch?v=K7iRfOs-aUw</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mprR3c_Y4pA</t>
+          <t>https://www.youtube.com/watch?v=bI8Ry6GhMSE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gT8v8Zq8hS8</t>
+          <t>https://www.youtube.com/watch?v=GeGxgmPTe4c</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Kz_z7QxsmG0</t>
+          <t>https://www.youtube.com/watch?v=5faMjKuB9bc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=UF9Iqmg94tk</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/watch?v=zaRkONvyGr8</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=tHEyzVbl4bg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=EWS_CIxttVw</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/watch?v=xpDnVSmNFX0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=M7WzV8C3v-Y</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=LQuuoHTyYz8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/watch?v=K0Ta65OqQkY</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=sCR3Xh8Jpxg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Xh7b_KqQvI8</t>
+          <t>https://www.youtube.com/watch?v=4NB0NDtOwIQ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1vL3MXva9ms</t>
+          <t>https://www.youtube.com/watch?v=7By4AEHk9zM</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=G1rOthIU-uo</t>
+          <t>https://www.youtube.com/watch?v=U3RkDLtS7uY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6ph8iY7Z2lU</t>
+          <t>https://www.youtube.com/watch?v=dGAgxozNWFE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=S6ifbS1wO60</t>
+          <t>https://www.youtube.com/watch?v=R0UkJSzM_4k</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R0UkJSzM_4k</t>
+          <t>https://www.youtube.com/watch?v=783pPli9yQ8</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=d_6w4v3u2Hk</t>
+          <t>https://www.youtube.com/watch?v=1nENigGr-a0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VbTx6j_Fq-8</t>
+          <t>https://www.youtube.com/watch?v=U3RkDLtS7uY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yYw_2F0O46Q</t>
+          <t>https://www.youtube.com/watch?v=pTB30aXS77U</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pTB30aXS77U</t>
+          <t>https://www.youtube.com/watch?v=DMZ5r0A31f4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=v-27FT7-5pk</t>
+          <t>https://www.youtube.com/watch?v=J1f5b4vcxCQ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TMuno5_b7Qk</t>
+          <t>https://www.youtube.com/watch?v=0y_PRGk_1-k</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EJavaYOFgkE</t>
+          <t>https://www.youtube.com/watch?v=PPup1yeU45I</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PPup1yeU45I</t>
+          <t>https://www.youtube.com/watch?v=ub0DXaeV6hA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=v9ejT8FO-7I</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/watch?v=M7Xi1yO_58o</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=v9ejT8FO-7I</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CRGPbCbRpHU</t>
+          <t>https://www.youtube.com/watch?v=FU4WlwfS3G0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FU4WlwfS3G0</t>
+          <t>https://www.youtube.com/watch?v=1nENigGr-a0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=S2y9_710_0Q</t>
+          <t>https://www.youtube.com/watch?v=KmAyPUv97nM</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KmAyPUv97nM</t>
+          <t>https://www.youtube.com/watch?v=1nENigGr-a0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
+          <t>https://www.youtube.com/watch?v=umWABit-wbk</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>https://www.youtube.com/watch?v=Tp8KpMe-ZKw</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/watch?v=umWABit-wbk</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">

--- a/System_Design_Roadmap.xlsx
+++ b/System_Design_Roadmap.xlsx
@@ -542,10 +542,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Completed</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -591,7 +590,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -637,7 +635,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -683,7 +680,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -729,7 +725,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -775,7 +770,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -821,7 +815,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -867,7 +860,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -913,7 +905,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -959,7 +950,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1005,7 +995,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1051,7 +1040,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1097,7 +1085,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1143,7 +1130,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1189,7 +1175,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1235,7 +1220,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1281,7 +1265,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1327,7 +1310,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1373,7 +1355,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1419,7 +1400,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1465,7 +1445,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1511,7 +1490,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1557,7 +1535,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1603,7 +1580,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1649,7 +1625,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1695,7 +1670,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1741,7 +1715,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1787,7 +1760,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1833,7 +1805,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1879,7 +1850,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1925,7 +1895,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1971,7 +1940,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2017,7 +1985,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2063,7 +2030,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2109,7 +2075,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2155,7 +2120,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2201,7 +2165,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2247,7 +2210,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2293,7 +2255,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2339,7 +2300,6 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/System_Design_Roadmap.xlsx
+++ b/System_Design_Roadmap.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
